--- a/docs/examples/ftse_outcomes_synthetic.xlsx
+++ b/docs/examples/ftse_outcomes_synthetic.xlsx
@@ -81,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -100,7 +100,6 @@
     <xf numFmtId="164" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -615,7 +614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -648,14 +647,14 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated SYNTHETIC FIXTURE: no observed market performance. The live mock trader enters ideas as they trigger during the day: one new trade per scan, up to 5 a day (3 a day before 23 Oct 2026), one per share, FTSE 100 shares only from 23 Oct 2026, and only ideas that pass the entry rules, including the check that the target would pay more than the stop could cost after costs. Each entry was saved the moment the scan ran (scan_data/live_mock_trades.csv) and is filled at the open of the next 15-minute candle. Trades close at the target, the stop, or the end of the day.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
+          <t>Generated SYNTHETIC FIXTURE: no observed market performance. The live mock trader enters ideas as they trigger during the day: every idea that passes the rules, up to 5 open at once and 10 a day (before 26 Oct 2026: 1 new trade per scan and 5 a day; before 23 Oct: 3 a day), one per share, FTSE 100 shares only from 23 Oct 2026, and only ideas that pass the entry rules, including the check that the target would pay more than the stop could cost after costs. Each entry was saved the moment the scan ran (scan_data/live_mock_trades.csv) and is filled at the open of the next 15-minute candle. Trades close at the target, the stop, or the end of the day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Each trade is £100. Dealing costs = 0.10% (buy and sell together); stamp duty = 0.50% on buys of real shares (sells never pay it). Grey rows were never entered or have no result yet.</t>
+          <t>Each trade is £100. Dealing costs = 0.10% (buy and sell together); stamp duty = 0.50% on buys (0 = spread bet, the basis for all results from 26 Oct 2026, including earlier trades). Only completed trades are listed: skipped trades and those without a result yet are left out. Results rechecked with version 3 missing-price safeguards; older totals may differ. Only resolved trades enter the totals.</t>
         </is>
       </c>
     </row>
@@ -687,20 +686,15 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Not resolved / skipped</t>
+          <t>Gross profit / loss (£)</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Gross profit / loss (£)</t>
+          <t>Dealing costs (£)</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Dealing costs (£)</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Stamp duty (£)</t>
         </is>
@@ -722,16 +716,13 @@
       <c r="E5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="1" t="n">
-        <v>3</v>
+      <c r="F5" s="4" t="n">
+        <v>2.7</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>2.7</v>
+        <v>-0.4</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="I5" s="4" t="n">
         <v>-1.5</v>
       </c>
     </row>
@@ -1174,151 +1165,6 @@
       </c>
       <c r="R16" s="11" t="n">
         <v>0.8</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Synthetic example 6</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>DEMO5.L</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="I17" s="12" t="n">
-        <v>98</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>106</v>
-      </c>
-      <c r="K17" s="12" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Synthetic example 7</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>DEMO6.L</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>Breakout</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n">
-        <v>98</v>
-      </c>
-      <c r="J18" s="12" t="n">
-        <v>106</v>
-      </c>
-      <c r="K18" s="12" t="inlineStr">
-        <is>
-          <t>Not resolved yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Synthetic example 5</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>DEMO4.L</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>Breakout</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="I19" s="12" t="n">
-        <v>98</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>106</v>
-      </c>
-      <c r="K19" s="12" t="inlineStr">
-        <is>
-          <t>Skipped (price already past stop or target)</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -1352,7 +1198,7 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>Live: trades at trigger points (up to 5 a day) (cumulative £)</t>
+          <t>Live: trades at trigger points (cumulative £)</t>
         </is>
       </c>
     </row>

--- a/docs/examples/ftse_outcomes_synthetic.xlsx
+++ b/docs/examples/ftse_outcomes_synthetic.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live Mock Trades" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,8 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;£&quot;#,##0.00;[Red]-&quot;£&quot;#,##0.00;&quot;£&quot;0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
+    <numFmt numFmtId="165" formatCode="&quot;£&quot;#,##0.00;[Red]-&quot;£&quot;#,##0.00;&quot;£&quot;0.00"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -31,27 +33,22 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -81,25 +78,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -614,565 +613,452 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Live mock trades (paper only, no real orders)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Generated SYNTHETIC FIXTURE: no observed market performance. The live mock trader enters ideas as they trigger during the day: every idea that passes the rules, up to 5 open at once and 10 a day (before 26 Oct 2026: 1 new trade per scan and 5 a day; before 23 Oct: 3 a day), one per share, FTSE 100 shares only from 23 Oct 2026, and only ideas that pass the entry rules, including the check that the target would pay more than the stop could cost after costs. Each entry was saved the moment the scan ran (scan_data/live_mock_trades.csv) and is filled at the open of the next 15-minute candle. Trades close at the target, the stop, or the end of the day.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Each trade is £100. Dealing costs = 0.10% (buy and sell together); stamp duty = 0.50% on buys (0 = spread bet, the basis for all results from 26 Oct 2026, including earlier trades). Only completed trades are listed: skipped trades and those without a result yet are left out. Results rechecked with version 3 missing-price safeguards; older totals may differ. Only resolved trades enter the totals.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Net after all fees (£)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+          <t>Net after costs £</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Profitable</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Losing</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Lost</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Flat</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Gross profit / loss (£)</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Dealing costs (£)</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Stamp duty (£)</t>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg per trade £</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Every idea: avg £</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Difference £</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>SYNTHETIC EXAMPLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Trade</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>Stop %</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>Exit</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>Before £</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>Costs £</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>After £</t>
+        </is>
+      </c>
+      <c r="P4" s="1" t="inlineStr">
+        <is>
+          <t>Running £</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Synthetic example 1</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>DEMO0.L</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Reclaim</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>Target hit</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>09-14 15:00</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="O5" s="6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic example 2</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>DEMO1.L</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>115</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>Target hit</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>09-14 15:00</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N6" s="9" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="O6" s="9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P6" s="9" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic example 4</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>DEMO3.L</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>109</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>End of day</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>09-15 15:00</t>
+        </is>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N7" s="9" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="O7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="9" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic example 3</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>DEMO2.L</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Reclaim</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>105</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>09-15 15:00</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="N8" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O8" s="9" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="P8" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="B5" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Comparison</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Average per trade (£)</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Every idea: completed</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Every idea: average per trade (£)</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Difference (£)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Live trades vs every idea</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Every idea = the first sighting each day of every idea the scanner flagged (all shares, before the entry rules), traded the same way with the same costs. If the live trades don't beat it, the entry rules aren't helping. With fewer than about 100 completed trades the difference is mostly luck.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Signal time</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Trade no.</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Direction</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Setup</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Entry</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>Exit time</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>Amount traded (£)</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>Gross profit / loss (£)</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>Dealing costs (£)</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>Stamp duty (£)</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t>Net after all fees (£)</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t>Realised running net (£)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Synthetic example 1</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>DEMO0.L</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>Breakout</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="I13" s="8" t="n">
-        <v>98</v>
-      </c>
-      <c r="J13" s="8" t="n">
-        <v>106</v>
-      </c>
-      <c r="K13" s="8" t="inlineStr">
-        <is>
-          <t>Target hit</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-14 15:00</t>
-        </is>
-      </c>
-      <c r="M13" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="N13" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="O13" s="9" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="P13" s="9" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="Q13" s="9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="R13" s="9" t="n">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Synthetic example 2</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>DEMO1.L</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="I14" s="10" t="n">
-        <v>95</v>
-      </c>
-      <c r="J14" s="10" t="n">
-        <v>115</v>
-      </c>
-      <c r="K14" s="10" t="inlineStr">
-        <is>
-          <t>Target hit</t>
-        </is>
-      </c>
-      <c r="L14" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-14 15:00</t>
-        </is>
-      </c>
-      <c r="M14" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="N14" s="11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O14" s="11" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="P14" s="11" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="Q14" s="11" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="R14" s="11" t="n">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Synthetic example 4</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>DEMO3.L</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="I15" s="10" t="n">
-        <v>97</v>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v>109</v>
-      </c>
-      <c r="K15" s="10" t="inlineStr">
-        <is>
-          <t>Closed at end of day</t>
-        </is>
-      </c>
-      <c r="L15" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-15 15:00</t>
-        </is>
-      </c>
-      <c r="M15" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="N15" s="11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O15" s="11" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="P15" s="11" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="Q15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="11" t="n">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Synthetic example 3</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>DEMO2.L</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>Breakout</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="I16" s="10" t="n">
-        <v>105</v>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v>85</v>
-      </c>
-      <c r="K16" s="10" t="inlineStr">
-        <is>
-          <t>Stopped out</t>
-        </is>
-      </c>
-      <c r="L16" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-15 15:00</t>
-        </is>
-      </c>
-      <c r="M16" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="N16" s="11" t="n">
-        <v>-4</v>
-      </c>
-      <c r="O16" s="11" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="P16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="11" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="R16" s="11" t="n">
-        <v>0.8</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:R3"/>
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A9:R9"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1191,41 +1077,41 @@
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Live: trades at trigger points (cumulative £)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="11" t="n">
         <v>4.9</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="11" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="4"/>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Each trade is £100, after dealing costs and stamp duty.</t>
         </is>
@@ -1235,4 +1121,118 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Explanation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Live mock trades</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Paper only, no real orders. Generated SYNTHETIC EXAMPLE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>How trades are chosen</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Every idea that passes the scanner's rules, up to 5 open at once and 10 a day (skipped trades don't count), FTSE 100 shares only; one trade per share a day, though a share skipped at entry can be tried again. History: before 26 Oct 2026 one new trade per scan and 5 a day; before 23 Oct 3 a day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Entry and exit</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Each entry is saved the moment the scan runs (scan_data/live_mock_trades.csv) and filled at the open of the next 15-minute candle. From 28 Oct a trade is skipped if that price leaves less than half the planned room to the stop. Trades close at the target, the stop, or the end of the day (16:30).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>£100 a trade. 0.10% dealing (buy and sell together); stamp duty 0.50% on buys (0 = spread bet, the basis for all results from 26 Oct 2026, including earlier trades).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>What is listed</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Completed trades only: skipped trades and those without a result yet are left out, and only completed trades enter the totals. Results use the version 3 missing-price safeguards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Stop %</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Room between the entry price and the stop, as a % of the entry price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Every idea</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>The first sighting each day of every idea the scanner flagged (all shares, before the entry rules), traded the same way with the same costs. If the live trades don't beat it, the entry rules aren't helping. With fewer than about 100 completed trades the difference is mostly luck.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>